--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484735_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484735_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4384</v>
+        <v>5.852</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2665</v>
+        <v>2.8969</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1719</v>
+        <v>2.955</v>
       </c>
       <c r="G2" t="n">
         <v>3.5871</v>
@@ -610,13 +610,13 @@
         <v>2.0757</v>
       </c>
       <c r="S2" t="n">
-        <v>4.0028</v>
+        <v>2.4163</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4566</v>
+        <v>1.087</v>
       </c>
       <c r="U2" t="n">
-        <v>2.5462</v>
+        <v>1.3293</v>
       </c>
       <c r="V2" t="n">
         <v>2.4904</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. ALBALADEJO PEREZ</t>
+          <t>P. LOPEZ-VALVERDE CARRASCO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9439</v>
+        <v>3.2722</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.264</v>
+        <v>0.2747</v>
       </c>
       <c r="F3" t="n">
-        <v>3.208</v>
+        <v>2.9975</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1106</v>
+        <v>1.1413</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4523</v>
+        <v>2.9856</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5629</v>
+        <v>-1.8443</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5395</v>
+        <v>0.7326</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.8642</v>
+        <v>2.599</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3247</v>
+        <v>-1.8664</v>
       </c>
       <c r="M3" t="n">
-        <v>1.6501</v>
+        <v>0.4087</v>
       </c>
       <c r="N3" t="n">
-        <v>1.4118</v>
+        <v>0.3866</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2383</v>
+        <v>0.0221</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5661</v>
+        <v>2.0757</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3209</v>
+        <v>3.0192</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8524</v>
+        <v>0.0552</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.1838</v>
       </c>
       <c r="U3" t="n">
-        <v>0.237</v>
+        <v>-0.1286</v>
       </c>
       <c r="V3" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.547</v>
+        <v>0.3018</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. GALVEZ ARROYO</t>
+          <t>N. ALBALADEJO PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2965</v>
+        <v>2.9091</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2013</v>
+        <v>-0.1666</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4979</v>
+        <v>3.0757</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1101</v>
+        <v>1.1106</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4866</v>
+        <v>-0.4523</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6235000000000001</v>
+        <v>1.5629</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3509</v>
+        <v>-0.5395</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7495</v>
+        <v>-1.8642</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6014</v>
+        <v>1.3247</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2408</v>
+        <v>1.6501</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2629</v>
+        <v>1.4118</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0221</v>
+        <v>0.2383</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.9627</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q4" t="n">
-        <v>-6.6045</v>
+        <v>-1.887</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6418</v>
+        <v>1.3209</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2058</v>
+        <v>0.8176</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4296</v>
+        <v>0.7129</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2239</v>
+        <v>0.1047</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9434</v>
+        <v>1.547</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6226</v>
+        <v>1.547</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. LOPEZ-VALVERDE CARRASCO</t>
+          <t>S. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7692</v>
+        <v>2.3826</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7786</v>
+        <v>-0.5121</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5478</v>
+        <v>2.8947</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1413</v>
+        <v>5.1101</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9856</v>
+        <v>4.4866</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8443</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7326</v>
+        <v>5.3509</v>
       </c>
       <c r="K5" t="n">
-        <v>2.599</v>
+        <v>4.7495</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.8664</v>
+        <v>0.6014</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4087</v>
+        <v>-0.2408</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3866</v>
+        <v>-0.2629</v>
       </c>
       <c r="O5" t="n">
         <v>0.0221</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0757</v>
+        <v>-3.9627</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9435</v>
+        <v>-6.6045</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0192</v>
+        <v>2.6418</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4478</v>
+        <v>0.2918</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8695000000000001</v>
+        <v>0.1188</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5784</v>
+        <v>0.1729</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.9434</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3018</v>
+        <v>0.6226</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3018</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9182</v>
+        <v>1.617</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8416</v>
+        <v>-1.3544</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7598</v>
+        <v>2.9714</v>
       </c>
       <c r="G6" t="n">
         <v>2.3012</v>
@@ -922,13 +922,13 @@
         <v>1.3209</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4961</v>
+        <v>0.2027</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0218</v>
+        <v>0.4654</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4744</v>
+        <v>-0.2627</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3208</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.5964</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.451</v>
+        <v>-2.5669</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6531</v>
+        <v>1.9705</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5941</v>
@@ -1000,13 +1000,13 @@
         <v>2.4531</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2116</v>
+        <v>0.4131</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6895</v>
+        <v>0.5735</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4778</v>
+        <v>-0.1604</v>
       </c>
       <c r="V7" t="n">
         <v>0.9054</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9302</v>
+        <v>-2.0314</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0283</v>
+        <v>-1.2618</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9018</v>
+        <v>-0.7696</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3029</v>
@@ -1078,13 +1078,13 @@
         <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7501</v>
+        <v>0.6488</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3826</v>
+        <v>1.1491</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6325</v>
+        <v>-0.5002</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2452</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2257</v>
+        <v>-2.1106</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7042</v>
+        <v>-3.4304</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4786</v>
+        <v>1.3198</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7691</v>
@@ -1156,13 +1156,13 @@
         <v>1.5096</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5626</v>
+        <v>0.6777</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1205</v>
+        <v>0.3943</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4421</v>
+        <v>0.2834</v>
       </c>
       <c r="V9" t="n">
         <v>1.2452</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>10.4124</v>
+        <v>11.2945</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.0025</v>
+        <v>-6.1206</v>
       </c>
       <c r="F10" t="n">
-        <v>17.4153</v>
+        <v>17.415</v>
       </c>
       <c r="G10" t="n">
         <v>10.5842</v>
@@ -1210,7 +1210,7 @@
         <v>6.349200000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>9.273500000000002</v>
+        <v>9.273499999999999</v>
       </c>
       <c r="L10" t="n">
         <v>-2.9244</v>
@@ -1234,13 +1234,13 @@
         <v>15.096</v>
       </c>
       <c r="S10" t="n">
-        <v>4.6414</v>
+        <v>5.5232</v>
       </c>
       <c r="T10" t="n">
-        <v>3.8029</v>
+        <v>4.6848</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8383</v>
+        <v>0.8384</v>
       </c>
       <c r="V10" t="n">
         <v>5.5654</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2.3866</v>
+        <v>2.7968</v>
       </c>
       <c r="E11" t="n">
-        <v>0.713</v>
+        <v>0.8104</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6737</v>
+        <v>1.9864</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8425</v>
@@ -1312,13 +1312,13 @@
         <v>3.0192</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0917</v>
+        <v>0.3184</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.09</v>
+        <v>0.0074</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0017</v>
+        <v>0.311</v>
       </c>
       <c r="V11" t="n">
         <v>1.2452</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.2227</v>
+        <v>2.4537</v>
       </c>
       <c r="E12" t="n">
         <v>0.4368</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7859</v>
+        <v>2.0169</v>
       </c>
       <c r="G12" t="n">
         <v>1.6098</v>
@@ -1390,13 +1390,13 @@
         <v>3.5853</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1787</v>
+        <v>0.4097</v>
       </c>
       <c r="T12" t="n">
         <v>0.3955</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2169</v>
+        <v>0.0142</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2076</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W. LADSON BUGALLO</t>
+          <t>D. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.642</v>
+        <v>1.6563</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0399</v>
+        <v>-0.1265</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6021</v>
+        <v>1.7828</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5377</v>
+        <v>3.1035</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2154</v>
+        <v>-0.9031</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6776</v>
+        <v>4.0067</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1758</v>
+        <v>4.2974</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1261</v>
+        <v>1.1786</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0496</v>
+        <v>3.1188</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7135</v>
+        <v>-1.1939</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.3415</v>
+        <v>-2.0817</v>
       </c>
       <c r="O13" t="n">
-        <v>0.628</v>
+        <v>0.8878</v>
       </c>
       <c r="P13" t="n">
-        <v>2.0757</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.887</v>
+        <v>-4.7175</v>
       </c>
       <c r="R13" t="n">
-        <v>3.9627</v>
+        <v>3.3966</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7077</v>
+        <v>-0.1263</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7512</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0435</v>
+        <v>-0.1181</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6036</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. HOLGADO CUELLAR</t>
+          <t>W. LADSON BUGALLO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.073</v>
+        <v>1.4699</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.029</v>
+        <v>-0.4473</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1021</v>
+        <v>1.9172</v>
       </c>
       <c r="G14" t="n">
-        <v>3.1035</v>
+        <v>-0.5377</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9031</v>
+        <v>-1.2154</v>
       </c>
       <c r="I14" t="n">
-        <v>4.0067</v>
+        <v>0.6776</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2974</v>
+        <v>1.1758</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1786</v>
+        <v>1.1261</v>
       </c>
       <c r="L14" t="n">
-        <v>3.1188</v>
+        <v>0.0496</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1939</v>
+        <v>-1.7135</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0817</v>
+        <v>-2.3415</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8878</v>
+        <v>0.628</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.3209</v>
+        <v>2.0757</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.7175</v>
+        <v>-1.887</v>
       </c>
       <c r="R14" t="n">
-        <v>3.3966</v>
+        <v>3.9627</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7096</v>
+        <v>0.5356</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0893</v>
+        <v>0.264</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7988</v>
+        <v>0.2716</v>
       </c>
       <c r="V14" t="n">
+        <v>-0.6036</v>
+      </c>
+      <c r="W14" t="n">
         <v>0</v>
       </c>
-      <c r="W14" t="n">
-        <v>0.3018</v>
-      </c>
       <c r="X14" t="n">
-        <v>-0.3018</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.852</v>
+        <v>1.0733</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1835</v>
+        <v>1.3784</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3316</v>
+        <v>-0.3051</v>
       </c>
       <c r="G15" t="n">
         <v>0.4446</v>
@@ -1624,13 +1624,13 @@
         <v>0.5661</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1587</v>
+        <v>0.0626</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1764</v>
+        <v>0.0185</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6694</v>
+        <v>0.7933</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.024</v>
+        <v>0.0735</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6933</v>
+        <v>0.7198</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5223</v>
@@ -1702,13 +1702,13 @@
         <v>1.1322</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1857</v>
+        <v>-1.0618</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4115</v>
+        <v>-0.3141</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7742</v>
+        <v>-0.7477</v>
       </c>
       <c r="V16" t="n">
         <v>1.2452</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3882</v>
+        <v>0.4147</v>
       </c>
       <c r="E17" t="n">
         <v>0.0746</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3136</v>
+        <v>0.3401</v>
       </c>
       <c r="G17" t="n">
         <v>0.6304</v>
@@ -1780,13 +1780,13 @@
         <v>0.3774</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6196</v>
+        <v>-0.5931</v>
       </c>
       <c r="T17" t="n">
         <v>0.0123</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6319</v>
+        <v>-0.6055</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3314</v>
+        <v>-2.0933</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4962</v>
+        <v>-2.886</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1649</v>
+        <v>0.7927</v>
       </c>
       <c r="G18" t="n">
         <v>-2.4258</v>
@@ -1858,13 +1858,13 @@
         <v>2.8305</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8871</v>
+        <v>-0.649</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1945</v>
+        <v>-0.1952</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0816</v>
+        <v>-0.4538</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9054</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5863</v>
+        <v>-3.3553</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0376</v>
+        <v>-1.6479</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5487</v>
+        <v>-1.7074</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8522999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>1.5096</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4514</v>
+        <v>-1.2204</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.823</v>
+        <v>-0.4333</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6284</v>
+        <v>-0.7871</v>
       </c>
       <c r="V19" t="n">
         <v>-2.7922</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.31</v>
+        <v>-6.2196</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.7307</v>
+        <v>-5.6333</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5793</v>
+        <v>-0.5864</v>
       </c>
       <c r="G20" t="n">
         <v>-3.7318</v>
@@ -2014,13 +2014,13 @@
         <v>1.5096</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3139</v>
+        <v>-0.2235</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2787</v>
+        <v>-0.1813</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0352</v>
+        <v>-0.0423</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9434</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.4189</v>
+        <v>-7.4537</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.545400000000001</v>
+        <v>-9.447900000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1265</v>
+        <v>1.9942</v>
       </c>
       <c r="G21" t="n">
         <v>-7.4601</v>
@@ -2092,13 +2092,13 @@
         <v>3.5853</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.11</v>
+        <v>-0.1448</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-0.4041</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3916</v>
+        <v>0.2593</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6036</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.4127</v>
+        <v>-8.463899999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-17.4151</v>
+        <v>-17.4152</v>
       </c>
       <c r="F22" t="n">
-        <v>7.0025</v>
+        <v>8.9512</v>
       </c>
       <c r="G22" t="n">
         <v>-10.5842</v>
@@ -2170,13 +2170,13 @@
         <v>25.4745</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.6413</v>
+        <v>-2.6926</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8383</v>
+        <v>-0.8384999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.802999999999999</v>
+        <v>-1.8543</v>
       </c>
       <c r="V22" t="n">
         <v>-5.5654</v>
